--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>204</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>173</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>346</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.73333333</v>
+        <v>0.99333333</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.54111406</v>
+        <v>0.98290598</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.88311688</v>
+        <v>0.995671</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.67105263</v>
+        <v>0.98924731</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.833333333333333</v>
+        <v>0.998666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.77319587628866</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.649350649350649</v>
+        <v>0.995670995670996</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.705882352941177</v>
+        <v>0.997830802603037</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.880130787645239</v>
+        <v>0.999908248463162</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>230</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>236</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>515</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.99333333</v>
+        <v>0.664</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.98290598</v>
+        <v>0.4767184</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.995671</v>
+        <v>0.93073593</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.98924731</v>
+        <v>0.63049853</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.998666666666667</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.766666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.995670995670996</v>
+        <v>0.597402597402597</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.997830802603037</v>
+        <v>0.671532846715329</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.51</v>
+        <v>0.77</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.999908248463162</v>
+        <v>0.875409754022471</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>236</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>283</v>
+        <v>512</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.664</v>
+        <v>0.984</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.4767184</v>
+        <v>0.96995708</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.93073593</v>
+        <v>0.97835498</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.63049853</v>
+        <v>0.97413793</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.82</v>
+        <v>0.985333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.766666666666667</v>
+        <v>0.966101694915254</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.597402597402597</v>
+        <v>0.987012987012987</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.671532846715329</v>
+        <v>0.97644539614561</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.77</v>
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.875409754022471</v>
+        <v>0.998744672155077</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>7</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>512</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.984</v>
+        <v>0.61466667</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.96995708</v>
+        <v>0.44268775</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.97835498</v>
+        <v>0.96969697</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.97413793</v>
+        <v>0.60786974</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.985333333333333</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.966101694915254</v>
+        <v>0.738197424892704</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.987012987012987</v>
+        <v>0.744588744588745</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.97644539614561</v>
+        <v>0.741379310344828</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.49</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.998744672155077</v>
+        <v>0.886428279491863</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>237</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>231</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.61466667</v>
+        <v>0.692</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.44268775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.96969697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.60786974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.84</v>
+        <v>0.705333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.738197424892704</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.744588744588745</v>
+        <v>0.0432900432900433</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.741379310344828</v>
+        <v>0.0829875518672199</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.76</v>
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.886428279491863</v>
+        <v>0.542301629006831</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.692</v>
+        <v>0.69333333</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.55555556</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.02164502</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.04166667</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.705333333333333</v>
+        <v>0.728</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0.601503759398496</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.0432900432900433</v>
+        <v>0.346320346320346</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.0829875518672199</v>
+        <v>0.43956043956044</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.542301629006831</v>
+        <v>0.646439623318236</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>5</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>515</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>226</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.69333333</v>
+        <v>0.61466667</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.55555556</v>
+        <v>0.44268775</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02164502</v>
+        <v>0.96969697</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04166667</v>
+        <v>0.60786974</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.728</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.601503759398496</v>
+        <v>0.738197424892704</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.346320346320346</v>
+        <v>0.744588744588745</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.43956043956044</v>
+        <v>0.741379310344828</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.19</v>
+        <v>0.76</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.646439623318236</v>
+        <v>0.886428279491863</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>224</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>282</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>237</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.61466667</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.44268775</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0.96969697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.60786974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.84</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.738197424892704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.744588744588745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.741379310344828</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -803,7 +803,7 @@
         <v>11</v>
       </c>
       <c r="B6" t="n">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.886428279491863</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.666666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.666666666666667</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>0.333333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">

--- a/Rdata_predictions.xlsx
+++ b/Rdata_predictions.xlsx
@@ -679,7 +679,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -687,7 +687,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -695,7 +695,7 @@
         <v>4</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -711,7 +711,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="n">
-        <v>0.333333333333333</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -719,7 +719,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -727,7 +727,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -735,7 +735,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="10">
@@ -771,7 +771,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>0.333333333333333</v>
+        <v>0.833333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -779,7 +779,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>0.333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -787,7 +787,7 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -795,7 +795,7 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>0.5</v>
+        <v>0.666666666666667</v>
       </c>
     </row>
     <row r="6">
@@ -825,7 +825,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5</v>
+        <v>0.875</v>
       </c>
     </row>
   </sheetData>
